--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574907162</v>
+        <v>46157.93119036015</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119036015</v>
+        <v>46157.93184263034</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93184263034</v>
+        <v>46157.93406254454</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406254454</v>
+        <v>46157.93724273612</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724273612</v>
+        <v>46158.28222027839</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222027839</v>
+        <v>46158.29703225259</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29703225259</v>
+        <v>46158.29821864238</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821864238</v>
+        <v>46158.33392986812</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392986812</v>
+        <v>46158.36862770073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Майнгаст- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862770073</v>
+        <v>46158.37293743611</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
